--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -107,6 +107,9 @@
     <t>ROMERO FLORES JULIAN RAFAEL</t>
   </si>
   <si>
+    <t>VALLADOLID PEREZ JOSE MARIA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA MARTINEZ ESTEBAN</t>
   </si>
   <si>
@@ -233,6 +236,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VALLADOLID</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -327,6 +333,9 @@
   </si>
   <si>
     <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>JOSE MARIA</t>
   </si>
   <si>
     <t>ESTEBAN</t>
@@ -694,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2265,22 +2274,22 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G20">
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2328,22 +2337,22 @@
         <v>-1</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AB20">
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2354,84 +2363,173 @@
         <v>-1</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+      <c r="H21">
+        <v>6</v>
+      </c>
+      <c r="I21">
+        <v>-1</v>
+      </c>
+      <c r="J21">
+        <v>-1</v>
+      </c>
+      <c r="K21">
+        <v>-1</v>
+      </c>
+      <c r="L21">
+        <v>-1</v>
+      </c>
+      <c r="M21">
+        <v>-1</v>
+      </c>
+      <c r="N21">
+        <v>-1</v>
+      </c>
+      <c r="O21">
+        <v>-1</v>
+      </c>
+      <c r="P21">
+        <v>-1</v>
+      </c>
+      <c r="Q21">
+        <v>-1</v>
+      </c>
+      <c r="R21">
+        <v>-1</v>
+      </c>
+      <c r="S21">
+        <v>-1</v>
+      </c>
+      <c r="T21">
+        <v>-1</v>
+      </c>
+      <c r="U21">
+        <v>-1</v>
+      </c>
+      <c r="V21">
+        <v>-1</v>
+      </c>
+      <c r="W21">
+        <v>-1</v>
+      </c>
+      <c r="X21">
+        <v>6</v>
+      </c>
+      <c r="Y21">
+        <v>6</v>
+      </c>
+      <c r="Z21">
+        <v>6</v>
+      </c>
+      <c r="AA21">
+        <v>6</v>
+      </c>
+      <c r="AB21">
+        <v>-1</v>
+      </c>
+      <c r="AC21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>-1</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
         <v>4</v>
       </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
-      <c r="I21">
-        <v>-1</v>
-      </c>
-      <c r="J21">
-        <v>-1</v>
-      </c>
-      <c r="K21">
-        <v>-1</v>
-      </c>
-      <c r="L21">
-        <v>-1</v>
-      </c>
-      <c r="M21">
-        <v>-1</v>
-      </c>
-      <c r="N21">
-        <v>-1</v>
-      </c>
-      <c r="O21">
-        <v>-1</v>
-      </c>
-      <c r="P21">
-        <v>-1</v>
-      </c>
-      <c r="Q21">
-        <v>-1</v>
-      </c>
-      <c r="R21">
-        <v>-1</v>
-      </c>
-      <c r="S21">
-        <v>-1</v>
-      </c>
-      <c r="T21">
-        <v>-1</v>
-      </c>
-      <c r="U21">
-        <v>-1</v>
-      </c>
-      <c r="V21">
-        <v>-1</v>
-      </c>
-      <c r="W21">
-        <v>-1</v>
-      </c>
-      <c r="X21">
-        <v>5</v>
-      </c>
-      <c r="Y21">
-        <v>5</v>
-      </c>
-      <c r="Z21">
-        <v>5</v>
-      </c>
-      <c r="AA21">
-        <v>5</v>
-      </c>
-      <c r="AB21">
-        <v>-1</v>
-      </c>
-      <c r="AC21">
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+      <c r="I22">
+        <v>-1</v>
+      </c>
+      <c r="J22">
+        <v>-1</v>
+      </c>
+      <c r="K22">
+        <v>-1</v>
+      </c>
+      <c r="L22">
+        <v>-1</v>
+      </c>
+      <c r="M22">
+        <v>-1</v>
+      </c>
+      <c r="N22">
+        <v>-1</v>
+      </c>
+      <c r="O22">
+        <v>-1</v>
+      </c>
+      <c r="P22">
+        <v>-1</v>
+      </c>
+      <c r="Q22">
+        <v>-1</v>
+      </c>
+      <c r="R22">
+        <v>-1</v>
+      </c>
+      <c r="S22">
+        <v>-1</v>
+      </c>
+      <c r="T22">
+        <v>-1</v>
+      </c>
+      <c r="U22">
+        <v>-1</v>
+      </c>
+      <c r="V22">
+        <v>-1</v>
+      </c>
+      <c r="W22">
+        <v>-1</v>
+      </c>
+      <c r="X22">
+        <v>5</v>
+      </c>
+      <c r="Y22">
+        <v>5</v>
+      </c>
+      <c r="Z22">
+        <v>5</v>
+      </c>
+      <c r="AA22">
+        <v>5</v>
+      </c>
+      <c r="AB22">
+        <v>-1</v>
+      </c>
+      <c r="AC22">
         <v>5</v>
       </c>
     </row>
@@ -2448,97 +2546,121 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2550,95 +2672,131 @@
         <v>100</v>
       </c>
       <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>90</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
       <c r="I4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>90</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
-        <v>100</v>
-      </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
         <v>87.5</v>
       </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
       <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
         <v>90</v>
       </c>
-      <c r="F5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>75</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
         <v>87.5</v>
       </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
         <v>90</v>
       </c>
-      <c r="K5">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>75</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
-      <c r="M5">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>87.5</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>90</v>
       </c>
-      <c r="P5">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2653,13 +2811,13 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2674,21 +2832,39 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2703,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -2724,21 +2900,39 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -2753,13 +2947,13 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -2774,21 +2968,39 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -2803,13 +3015,13 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2824,21 +3036,39 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -2853,13 +3083,13 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2874,21 +3104,39 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2897,98 +3145,134 @@
         <v>100</v>
       </c>
       <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
         <v>95</v>
       </c>
-      <c r="F11">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>75</v>
       </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
       <c r="I11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
         <v>95</v>
       </c>
-      <c r="K11">
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>75</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>95</v>
       </c>
-      <c r="P11">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
         <v>87.5</v>
       </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
       <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
         <v>90</v>
       </c>
-      <c r="F12">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>80</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
         <v>87.5</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
-      <c r="J12">
+      <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
         <v>90</v>
       </c>
-      <c r="K12">
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>80</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>87.5</v>
       </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>90</v>
       </c>
-      <c r="P12">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3000,45 +3284,63 @@
         <v>100</v>
       </c>
       <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>80</v>
       </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>80</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3050,45 +3352,63 @@
         <v>100</v>
       </c>
       <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>95</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>95</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
+        <v>100</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -3100,45 +3420,63 @@
         <v>100</v>
       </c>
       <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>75</v>
       </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
-      <c r="H15">
-        <v>100</v>
-      </c>
       <c r="I15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>75</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -3150,45 +3488,63 @@
         <v>100</v>
       </c>
       <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>90</v>
       </c>
-      <c r="G16">
-        <v>100</v>
-      </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
       <c r="I16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>90</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -3203,13 +3559,13 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -3224,21 +3580,39 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3250,45 +3624,63 @@
         <v>100</v>
       </c>
       <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>90</v>
       </c>
-      <c r="G18">
-        <v>100</v>
-      </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
       <c r="I18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>90</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3300,95 +3692,131 @@
         <v>100</v>
       </c>
       <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>85</v>
       </c>
-      <c r="G19">
-        <v>100</v>
-      </c>
-      <c r="H19">
-        <v>100</v>
-      </c>
       <c r="I19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>85</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
       <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
+        <v>100</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -3397,47 +3825,133 @@
         <v>100</v>
       </c>
       <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22">
         <v>90</v>
       </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>100</v>
-      </c>
-      <c r="H21">
-        <v>100</v>
-      </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
-      <c r="J21">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
         <v>90</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>90</v>
       </c>
-      <c r="P21">
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3458,31 +3972,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3490,10 +4004,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3508,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2">
         <v>100</v>
@@ -3519,10 +4033,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3537,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
         <v>100</v>
@@ -3548,10 +4062,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -3560,19 +4074,19 @@
         <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="G4" s="2">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="H4">
         <v>5.7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3580,10 +4094,10 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -3592,19 +4106,19 @@
         <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="G5" s="2">
-        <v>33.3</v>
+        <v>31.6</v>
       </c>
       <c r="H5">
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3612,10 +4126,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>13</v>
@@ -3624,19 +4138,19 @@
         <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>72.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>27.8</v>
+        <v>26.3</v>
       </c>
       <c r="H6">
         <v>7.2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3644,10 +4158,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -3656,19 +4170,19 @@
         <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="G7" s="2">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="H7">
         <v>7.1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3676,10 +4190,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>14</v>
@@ -3688,27 +4202,27 @@
         <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="G8" s="2">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="H8">
         <v>6.4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -3730,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3739,16 +4253,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -3762,19 +4276,19 @@
         <v>23330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3782,19 +4296,19 @@
         <v>23330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3802,19 +4316,19 @@
         <v>23330051920319</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3822,19 +4336,19 @@
         <v>23330051920319</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3842,19 +4356,19 @@
         <v>23330051920287</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3862,19 +4376,19 @@
         <v>23330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3882,19 +4396,19 @@
         <v>23330051920288</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3902,19 +4416,19 @@
         <v>23330051920288</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3922,19 +4436,19 @@
         <v>23330051920289</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3942,19 +4456,19 @@
         <v>23330051920289</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3962,19 +4476,19 @@
         <v>23330051920290</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3982,19 +4496,19 @@
         <v>23330051920290</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4002,19 +4516,19 @@
         <v>23330051920325</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4022,19 +4536,19 @@
         <v>23330051920325</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4042,19 +4556,19 @@
         <v>23330051920342</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4062,19 +4576,19 @@
         <v>23330051920342</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4082,19 +4596,19 @@
         <v>23330051920291</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4102,19 +4616,19 @@
         <v>23330051920291</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4122,19 +4636,19 @@
         <v>23330051920300</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4142,19 +4656,19 @@
         <v>23330051920300</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4162,19 +4676,19 @@
         <v>23330051920302</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4182,19 +4696,19 @@
         <v>23330051920302</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4202,19 +4716,19 @@
         <v>23330051920331</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4222,19 +4736,19 @@
         <v>23330051920331</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4242,19 +4756,19 @@
         <v>23330051920303</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4262,19 +4776,19 @@
         <v>23330051920303</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4282,19 +4796,19 @@
         <v>23330051920304</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4302,19 +4816,19 @@
         <v>23330051920304</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4322,19 +4836,19 @@
         <v>23330051920323</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4342,19 +4856,19 @@
         <v>23330051920323</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4362,19 +4876,19 @@
         <v>23330051920332</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4382,56 +4896,56 @@
         <v>23330051920332</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>23330051920305</v>
+        <v>23330051920364</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>23330051920305</v>
+        <v>23330051920364</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
         <v>45</v>
@@ -4439,42 +4953,182 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>23330051920306</v>
+        <v>23330051920364</v>
       </c>
       <c r="B36" t="s">
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>23330051920306</v>
+        <v>23330051920364</v>
       </c>
       <c r="B37" t="s">
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>23330051920364</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>23330051920364</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>23330051920364</v>
+      </c>
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>23330051920305</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>23330051920305</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>23330051920306</v>
+      </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>23330051920306</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4493,22 +5147,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4519,19 +5173,19 @@
         <v>23330051920287</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4542,19 +5196,19 @@
         <v>23330051920287</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4565,19 +5219,19 @@
         <v>23330051920288</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4588,19 +5242,19 @@
         <v>23330051920288</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -4611,19 +5265,19 @@
         <v>23330051920290</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4634,19 +5288,19 @@
         <v>23330051920290</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4657,19 +5311,19 @@
         <v>23330051920325</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4680,19 +5334,19 @@
         <v>23330051920325</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -4703,19 +5357,19 @@
         <v>23330051920331</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -4726,19 +5380,19 @@
         <v>23330051920331</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -4749,19 +5403,19 @@
         <v>23330051920304</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -4772,19 +5426,19 @@
         <v>23330051920304</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -4795,19 +5449,19 @@
         <v>23330051920305</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -4818,19 +5472,19 @@
         <v>23330051920305</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15">
         <v>-1</v>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -155,27 +155,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -191,157 +191,55 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ARIAS</t>
+    <t>VALLADOLID</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JOSE MARIA</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>VALLADOLID</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZANAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>GIANCARLO</t>
   </si>
   <si>
     <t>ANA ISABEL</t>
   </si>
   <si>
-    <t>YUREN</t>
+    <t>SERGIO JOSUE</t>
   </si>
   <si>
     <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>JULIAN RAFAEL</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>JOSE MARIA</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
 </sst>
 </file>
@@ -847,7 +745,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -862,28 +760,28 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -910,10 +808,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -922,10 +820,10 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -936,7 +834,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -951,28 +849,28 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -999,10 +897,10 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1014,7 +912,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1025,7 +923,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -1040,28 +938,28 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1088,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1103,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1114,7 +1012,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -1129,28 +1027,28 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1177,10 +1075,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1192,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1203,7 +1101,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1218,28 +1116,28 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1266,13 +1164,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1281,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1292,7 +1190,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1307,28 +1205,28 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1355,22 +1253,22 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>6</v>
@@ -1381,7 +1279,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1396,28 +1294,28 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1444,10 +1342,10 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1459,7 +1357,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>9</v>
@@ -1470,7 +1368,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1485,28 +1383,28 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1533,7 +1431,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1545,10 +1443,10 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1559,7 +1457,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1574,28 +1472,28 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1622,10 +1520,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1637,7 +1535,7 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1648,7 +1546,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -1663,28 +1561,28 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1711,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1726,7 +1624,7 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1737,7 +1635,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1752,28 +1650,28 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1800,10 +1698,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1812,10 +1710,10 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1826,7 +1724,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1841,28 +1739,28 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1889,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1901,10 +1799,10 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1915,7 +1813,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1930,28 +1828,28 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1978,10 +1876,10 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1993,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2004,7 +1902,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>9</v>
@@ -2019,28 +1917,28 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2067,13 +1965,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>10</v>
@@ -2082,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2093,7 +1991,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -2108,28 +2006,28 @@
         <v>5</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2156,10 +2054,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2171,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2182,7 +2080,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -2197,28 +2095,28 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2245,7 +2143,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2260,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2271,43 +2169,43 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2334,22 +2232,22 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>-1</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>-1</v>
@@ -2360,7 +2258,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2375,28 +2273,28 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2423,10 +2321,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2438,7 +2336,7 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2449,7 +2347,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2464,28 +2362,28 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2512,10 +2410,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2527,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2660,7 +2558,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2675,19 +2573,19 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>90</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -2696,19 +2594,19 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>90</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2717,7 +2615,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
         <v>90</v>
@@ -2728,7 +2626,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2743,49 +2641,49 @@
         <v>90</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>75</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>75</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>75</v>
@@ -2796,7 +2694,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2811,13 +2709,13 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2832,13 +2730,13 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2853,7 +2751,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2864,7 +2762,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2879,13 +2777,13 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -2900,13 +2798,13 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2921,7 +2819,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -2932,7 +2830,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -2947,19 +2845,19 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -2968,19 +2866,19 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -2989,7 +2887,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3000,7 +2898,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -3015,13 +2913,13 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3036,13 +2934,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3057,7 +2955,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3068,7 +2966,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -3083,13 +2981,13 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3104,13 +3002,13 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3125,7 +3023,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3136,7 +3034,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3151,49 +3049,49 @@
         <v>95</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>75</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>75</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
         <v>75</v>
@@ -3204,7 +3102,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3219,49 +3117,49 @@
         <v>90</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>80</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>80</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
         <v>80</v>
@@ -3272,7 +3170,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3287,13 +3185,13 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>80</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3305,16 +3203,16 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>80</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3326,10 +3224,10 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>80</v>
@@ -3340,7 +3238,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3355,19 +3253,19 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>95</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -3376,19 +3274,19 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>95</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3397,7 +3295,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
         <v>95</v>
@@ -3408,7 +3306,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -3423,19 +3321,19 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>75</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3444,19 +3342,19 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>75</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3465,7 +3363,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
         <v>75</v>
@@ -3476,7 +3374,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -3491,19 +3389,19 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>90</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3512,19 +3410,19 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
         <v>90</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3533,7 +3431,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
         <v>90</v>
@@ -3544,7 +3442,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -3559,19 +3457,19 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3580,19 +3478,19 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3601,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -3612,7 +3510,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3627,13 +3525,13 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>90</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -3648,13 +3546,13 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>90</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3669,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
         <v>90</v>
@@ -3680,7 +3578,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3695,19 +3593,19 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>85</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -3716,19 +3614,19 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>85</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3737,7 +3635,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
         <v>85</v>
@@ -3748,64 +3646,64 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3816,7 +3714,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -3831,19 +3729,19 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -3852,19 +3750,19 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3873,7 +3771,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -3884,7 +3782,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -3899,49 +3797,49 @@
         <v>90</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4001,7 +3899,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -4010,27 +3908,30 @@
         <v>19</v>
       </c>
       <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>42.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -4039,27 +3940,30 @@
         <v>19</v>
       </c>
       <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2">
+        <v>63.2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>36.8</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -4068,30 +3972,30 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>47.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4100,19 +4004,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>63.2</v>
+        <v>73.7</v>
       </c>
       <c r="G5" s="2">
-        <v>31.6</v>
+        <v>21.1</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -4123,7 +4027,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4132,19 +4036,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>68.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G6" s="2">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -4155,7 +4059,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4164,30 +4068,30 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G7" s="2">
         <v>21.1</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -4196,25 +4100,25 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>73.7</v>
+        <v>84.2</v>
       </c>
       <c r="G8" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4244,7 +4148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4273,862 +4177,42 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920286</v>
+        <v>23330051920364</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920286</v>
+        <v>23330051920364</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920319</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920319</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920287</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920287</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920288</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920288</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920289</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920289</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920290</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920290</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920325</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920325</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920342</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920342</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920291</v>
-      </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920291</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920300</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920302</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920302</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920331</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920331</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920303</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920303</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920304</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920304</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920323</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920323</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920332</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920332</v>
-      </c>
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920364</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920364</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920364</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920364</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920364</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920364</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920364</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>23330051920305</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>23330051920305</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>23330051920306</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>23330051920306</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5138,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5170,324 +4254,209 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920287</v>
+        <v>23330051920319</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>45</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920287</v>
+        <v>23330051920319</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920288</v>
+        <v>23330051920300</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>45</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920288</v>
+        <v>23330051920300</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>46</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920290</v>
+        <v>23330051920302</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920290</v>
+        <v>23330051920302</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920325</v>
+        <v>23330051920332</v>
       </c>
       <c r="B8" t="s">
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920325</v>
+        <v>23330051920332</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920331</v>
+        <v>23330051920303</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>45</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920331</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920304</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920304</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920305</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920305</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -158,18 +158,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -191,55 +191,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VALLADOLID</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>JOSE MARIA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ANA ISABEL</t>
   </si>
   <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
     <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
   </si>
 </sst>
 </file>
@@ -775,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -784,7 +760,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -826,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -864,7 +840,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -873,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -906,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>5</v>
@@ -953,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -962,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1004,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1042,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1051,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1093,7 +1069,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1131,7 +1107,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1140,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1173,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1182,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1220,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1229,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1309,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1318,7 +1294,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1351,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1360,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1398,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1407,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1440,7 +1416,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1449,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1487,7 +1463,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1496,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1576,7 +1552,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1585,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1618,7 +1594,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1627,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1665,7 +1641,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1674,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1716,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1754,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1763,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1843,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1852,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1885,7 +1861,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -1932,7 +1908,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -1941,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1983,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2021,7 +1997,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2030,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2063,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -2072,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2110,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2119,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2178,7 +2154,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -2187,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>5</v>
@@ -2199,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2208,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2241,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>6</v>
@@ -2250,7 +2226,7 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2288,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -2297,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2330,7 +2306,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2377,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2386,7 +2362,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2597,7 +2573,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P4">
         <v>95</v>
@@ -2618,7 +2594,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2656,7 +2632,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M5">
         <v>95</v>
@@ -2665,7 +2641,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="P5">
         <v>85</v>
@@ -2677,7 +2653,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T5">
         <v>95</v>
@@ -2686,7 +2662,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>75</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3064,7 +3040,7 @@
         <v>72.7</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M11">
         <v>85</v>
@@ -3073,7 +3049,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="P11">
         <v>90</v>
@@ -3085,7 +3061,7 @@
         <v>72.7</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11">
         <v>85</v>
@@ -3094,7 +3070,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>75</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3132,7 +3108,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M12">
         <v>92.5</v>
@@ -3153,7 +3129,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T12">
         <v>92.5</v>
@@ -3200,7 +3176,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M13">
         <v>97.5</v>
@@ -3209,7 +3185,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="P13">
         <v>95</v>
@@ -3221,7 +3197,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T13">
         <v>97.5</v>
@@ -3230,7 +3206,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3277,7 +3253,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P14">
         <v>90</v>
@@ -3298,7 +3274,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3345,7 +3321,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="P15">
         <v>70</v>
@@ -3366,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>75</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3413,7 +3389,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P16">
         <v>90</v>
@@ -3434,7 +3410,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3472,7 +3448,7 @@
         <v>97.7</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3481,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P17">
         <v>90</v>
@@ -3493,7 +3469,7 @@
         <v>97.7</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -3502,7 +3478,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3549,7 +3525,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P18">
         <v>90</v>
@@ -3570,7 +3546,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3655,7 +3631,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -3664,7 +3640,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I20">
         <v>70</v>
@@ -3676,7 +3652,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -3685,7 +3661,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P20">
         <v>70</v>
@@ -3697,7 +3673,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -3706,7 +3682,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3744,7 +3720,7 @@
         <v>97.7</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -3753,7 +3729,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P21">
         <v>90</v>
@@ -3765,7 +3741,7 @@
         <v>97.7</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -3774,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -3812,7 +3788,7 @@
         <v>93.2</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M22">
         <v>95</v>
@@ -3821,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P22">
         <v>85</v>
@@ -3833,7 +3809,7 @@
         <v>93.2</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T22">
         <v>95</v>
@@ -3842,7 +3818,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
   </sheetData>
@@ -3931,7 +3907,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3940,19 +3916,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>63.2</v>
+        <v>47.4</v>
       </c>
       <c r="G3" s="2">
-        <v>36.8</v>
+        <v>52.6</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3963,7 +3939,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3972,19 +3948,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>68.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="G4" s="2">
-        <v>31.6</v>
+        <v>52.6</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3995,7 +3971,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4004,30 +3980,30 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>73.7</v>
+        <v>63.2</v>
       </c>
       <c r="G5" s="2">
-        <v>21.1</v>
+        <v>36.8</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4036,25 +4012,25 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>73.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>21.1</v>
+        <v>31.6</v>
       </c>
       <c r="H6">
         <v>6.4</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4148,7 +4124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4175,46 +4151,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920364</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920364</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4222,7 +4158,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4254,22 +4190,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920319</v>
+        <v>23330051920302</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4277,22 +4213,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920319</v>
+        <v>23330051920302</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4300,16 +4236,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920300</v>
+        <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
         <v>61</v>
       </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4323,139 +4259,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920300</v>
+        <v>23330051920305</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
         <v>65</v>
       </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>46</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920302</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920302</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920332</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920332</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920303</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -155,24 +155,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -191,28 +191,34 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
   </si>
   <si>
     <t>ESTEBAN</t>
@@ -766,19 +772,19 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -799,7 +805,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -855,19 +861,19 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -879,13 +885,13 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>8</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -944,19 +950,19 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -968,13 +974,13 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1033,19 +1039,19 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1122,19 +1128,19 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1143,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1155,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1211,19 +1217,19 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1241,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1300,19 +1306,19 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1333,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1389,19 +1395,19 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1478,19 +1484,19 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1502,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1511,7 +1517,7 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1567,19 +1573,19 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1591,13 +1597,13 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -1656,19 +1662,19 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1677,10 +1683,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1745,19 +1751,19 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1769,7 +1775,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1778,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1834,19 +1840,19 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1858,7 +1864,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -1867,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1923,19 +1929,19 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -1947,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>10</v>
@@ -2012,19 +2018,19 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2042,10 +2048,10 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2101,19 +2107,19 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2125,16 +2131,16 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2190,19 +2196,19 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2220,7 +2226,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2279,19 +2285,19 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2368,19 +2374,19 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2389,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2582,7 +2588,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2650,7 +2656,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S5">
         <v>96.90000000000001</v>
@@ -2854,13 +2860,13 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -2928,7 +2934,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3055,16 +3061,16 @@
         <v>90</v>
       </c>
       <c r="Q11">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R11">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="S11">
         <v>50</v>
       </c>
       <c r="T11">
-        <v>85</v>
+        <v>56.7</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -3126,13 +3132,13 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S12">
         <v>93.8</v>
       </c>
       <c r="T12">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -3200,7 +3206,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="T13">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -3262,7 +3268,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3330,7 +3336,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3398,7 +3404,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3466,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>96.90000000000001</v>
@@ -3540,7 +3546,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -3602,7 +3608,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3670,13 +3676,13 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>88.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -3738,13 +3744,13 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S21">
         <v>96.90000000000001</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -3806,13 +3812,13 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S22">
         <v>90.59999999999999</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -3875,7 +3881,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -3884,19 +3890,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>42.1</v>
+        <v>47.4</v>
       </c>
       <c r="G2" s="2">
-        <v>57.9</v>
+        <v>52.6</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3907,7 +3913,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3928,7 +3934,7 @@
         <v>52.6</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3939,7 +3945,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3948,19 +3954,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>47.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>52.6</v>
+        <v>31.6</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3971,7 +3977,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -3980,19 +3986,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>63.2</v>
+        <v>73.7</v>
       </c>
       <c r="G5" s="2">
-        <v>36.8</v>
+        <v>26.3</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4003,7 +4009,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4012,19 +4018,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>68.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>31.6</v>
+        <v>21.1</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4035,7 +4041,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4056,7 +4062,7 @@
         <v>21.1</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4088,7 +4094,7 @@
         <v>15.8</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4158,7 +4164,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4190,22 +4196,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920302</v>
+        <v>23330051920342</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4213,22 +4219,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920302</v>
+        <v>23330051920342</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4236,7 +4242,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920303</v>
+        <v>23330051920300</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -4245,10 +4251,10 @@
         <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>45</v>
@@ -4259,24 +4265,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920305</v>
+        <v>23330051920300</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>46</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920305</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -194,19 +194,31 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>ARIAS</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
+    <t>RIOS</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -215,10 +227,16 @@
     <t>YAMILET</t>
   </si>
   <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>GIANCARLO</t>
   </si>
   <si>
-    <t>MARIEL</t>
+    <t>NOHEMI ANGELICA</t>
   </si>
   <si>
     <t>ESTEBAN</t>
@@ -769,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -787,7 +805,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -858,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -876,7 +894,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -947,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -965,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1036,7 +1054,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1054,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1075,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1125,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1143,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1214,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1232,10 +1250,10 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1303,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1321,10 +1339,10 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1342,7 +1360,7 @@
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1392,7 +1410,7 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1410,7 +1428,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1481,7 +1499,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1499,10 +1517,10 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1570,7 +1588,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1588,7 +1606,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1609,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1659,7 +1677,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1677,10 +1695,10 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1748,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1766,7 +1784,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1837,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1855,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1876,7 +1894,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1926,7 +1944,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -1944,7 +1962,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1965,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2015,7 +2033,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2033,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2054,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2104,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2122,7 +2140,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2193,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -2211,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2282,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2300,10 +2318,10 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2371,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -2389,7 +2407,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2582,7 +2600,7 @@
         <v>95</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2650,7 +2668,7 @@
         <v>82.5</v>
       </c>
       <c r="P5">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -2718,7 +2736,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2854,7 +2872,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -2922,7 +2940,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3058,7 +3076,7 @@
         <v>37.5</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q11">
         <v>88.90000000000001</v>
@@ -3126,7 +3144,7 @@
         <v>80</v>
       </c>
       <c r="P12">
-        <v>70</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3194,7 +3212,7 @@
         <v>85</v>
       </c>
       <c r="P13">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3262,7 +3280,7 @@
         <v>92.5</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3330,7 +3348,7 @@
         <v>82.5</v>
       </c>
       <c r="P15">
-        <v>70</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3398,7 +3416,7 @@
         <v>95</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3466,7 +3484,7 @@
         <v>95</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3534,7 +3552,7 @@
         <v>95</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3602,7 +3620,7 @@
         <v>85</v>
       </c>
       <c r="P19">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -3670,7 +3688,7 @@
         <v>80</v>
       </c>
       <c r="P20">
-        <v>70</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3738,7 +3756,7 @@
         <v>97.5</v>
       </c>
       <c r="P21">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -3806,7 +3824,7 @@
         <v>92.5</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -3922,19 +3940,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
+        <v>52.6</v>
+      </c>
+      <c r="G3" s="2">
         <v>47.4</v>
       </c>
-      <c r="G3" s="2">
-        <v>52.6</v>
-      </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3966,7 +3984,7 @@
         <v>31.6</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4164,7 +4182,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4205,7 +4223,7 @@
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4228,7 +4246,7 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -4242,22 +4260,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920300</v>
+        <v>23330051920332</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4265,22 +4283,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920300</v>
+        <v>23330051920332</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4294,10 +4312,10 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -4311,16 +4329,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920305</v>
+        <v>23330051920300</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4329,6 +4347,52 @@
         <v>45</v>
       </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920303</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920305</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -2618,7 +2618,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2686,7 +2686,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>82.5</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2754,7 +2754,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2822,7 +2822,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -2890,7 +2890,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -2958,7 +2958,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3026,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3094,7 +3094,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>37.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3162,7 +3162,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>80</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3230,7 +3230,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>85</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3298,7 +3298,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3366,7 +3366,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>82.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3434,7 +3434,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3502,7 +3502,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3570,7 +3570,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3638,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3706,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>80</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3774,7 +3774,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>97.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -3842,7 +3842,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>92.5</v>
+        <v>90.5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -155,24 +155,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -191,55 +191,46 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>RIOS</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
   </si>
   <si>
     <t>YAMILET</t>
   </si>
   <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
     <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
   </si>
 </sst>
 </file>
@@ -796,7 +787,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -817,7 +808,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -885,7 +876,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -974,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1063,7 +1054,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1152,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1173,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1241,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1330,7 +1321,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1419,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1508,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1529,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1597,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1618,7 +1609,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -1686,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1707,7 +1698,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1775,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1864,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1953,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2042,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2063,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2131,7 +2122,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2152,7 +2143,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2220,7 +2211,7 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2309,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2330,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2398,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2677,7 +2668,7 @@
         <v>87.5</v>
       </c>
       <c r="S5">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T5">
         <v>95</v>
@@ -3085,7 +3076,7 @@
         <v>50</v>
       </c>
       <c r="S11">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T11">
         <v>56.7</v>
@@ -3153,7 +3144,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S12">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T12">
         <v>93.3</v>
@@ -3221,7 +3212,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
         <v>96.7</v>
@@ -3493,7 +3484,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S17">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -3697,7 +3688,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>70.8</v>
       </c>
       <c r="T20">
         <v>95</v>
@@ -3765,7 +3756,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S21">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T21">
         <v>96.7</v>
@@ -3833,7 +3824,7 @@
         <v>95.3</v>
       </c>
       <c r="S22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T22">
         <v>91.7</v>
@@ -3899,7 +3890,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -3908,19 +3899,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
+        <v>52.6</v>
+      </c>
+      <c r="G2" s="2">
         <v>47.4</v>
       </c>
-      <c r="G2" s="2">
-        <v>52.6</v>
-      </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3931,7 +3922,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3940,19 +3931,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>52.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3963,7 +3954,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3972,19 +3963,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>68.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G4" s="2">
-        <v>31.6</v>
+        <v>26.3</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3995,7 +3986,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4004,19 +3995,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4027,7 +4018,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4048,7 +4039,7 @@
         <v>21.1</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4059,7 +4050,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4068,16 +4059,16 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G7" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -4182,7 +4173,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4214,22 +4205,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920342</v>
+        <v>23330051920319</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4237,22 +4228,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920342</v>
+        <v>23330051920319</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4260,7 +4251,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920332</v>
+        <v>23330051920286</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -4269,13 +4260,13 @@
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4283,19 +4274,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920332</v>
+        <v>23330051920342</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>45</v>
@@ -4306,22 +4297,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920286</v>
+        <v>23330051920303</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4329,70 +4320,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920300</v>
+        <v>23330051920332</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920303</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920305</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -150,9 +153,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Rodríguez Román Leticia</t>
@@ -592,13 +592,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -609,35 +609,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,77 +667,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -757,72 +773,84 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
         <v>4</v>
       </c>
-      <c r="M4">
-        <v>7</v>
-      </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD4">
+        <v>7</v>
+      </c>
+      <c r="AE4">
+        <v>6</v>
+      </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -846,13 +874,13 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -861,57 +889,69 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>6</v>
+      </c>
+      <c r="AE5">
+        <v>7</v>
+      </c>
+      <c r="AF5">
+        <v>5</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -935,72 +975,84 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>8</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>10</v>
       </c>
       <c r="R6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>9</v>
+      </c>
+      <c r="AE6">
+        <v>9</v>
+      </c>
+      <c r="AF6">
+        <v>7</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -1024,72 +1076,84 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>8</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>10</v>
       </c>
       <c r="R7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <v>10</v>
+      </c>
+      <c r="AE7">
+        <v>10</v>
+      </c>
+      <c r="AF7">
+        <v>7</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1113,34 +1177,34 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1149,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1158,27 +1222,39 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>6</v>
+      </c>
+      <c r="AF8">
+        <v>5</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1202,16 +1278,16 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1220,16 +1296,16 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>10</v>
       </c>
       <c r="R9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1238,36 +1314,48 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>9</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1291,37 +1379,37 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>7</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
       </c>
       <c r="R10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1330,16 +1418,16 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1348,15 +1436,27 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
+        <v>9</v>
+      </c>
+      <c r="AF10">
+        <v>7</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -1380,17 +1480,17 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
       <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>5</v>
-      </c>
       <c r="M11">
         <v>5</v>
       </c>
@@ -1401,20 +1501,20 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R11">
+        <v>6</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
         <v>0</v>
       </c>
-      <c r="S11">
-        <v>5</v>
-      </c>
-      <c r="T11">
-        <v>5</v>
-      </c>
       <c r="U11">
         <v>5</v>
       </c>
@@ -1428,7 +1528,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1442,10 +1542,22 @@
       <c r="AC11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>5</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1469,55 +1581,55 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1529,12 +1641,24 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>6</v>
+      </c>
+      <c r="AF12">
+        <v>5</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1558,72 +1682,84 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>5</v>
       </c>
       <c r="N13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>6</v>
+      </c>
+      <c r="AE13">
+        <v>8</v>
+      </c>
+      <c r="AF13">
+        <v>6</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>7</v>
@@ -1647,72 +1783,84 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>7</v>
       </c>
       <c r="N14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD14">
+        <v>7</v>
+      </c>
+      <c r="AE14">
+        <v>8</v>
+      </c>
+      <c r="AF14">
+        <v>7</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -1736,72 +1884,84 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>6</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>7</v>
       </c>
       <c r="N15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>6</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>7</v>
+      </c>
+      <c r="AE15">
+        <v>8</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -1825,72 +1985,84 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
       <c r="M16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>8</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>8</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD16">
+        <v>8</v>
+      </c>
+      <c r="AE16">
+        <v>7</v>
+      </c>
+      <c r="AF16">
+        <v>5</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -1914,72 +2086,84 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>9</v>
+      </c>
+      <c r="AE17">
+        <v>10</v>
+      </c>
+      <c r="AF17">
+        <v>6</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2003,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2012,22 +2196,22 @@
         <v>6</v>
       </c>
       <c r="L18">
+        <v>6</v>
+      </c>
+      <c r="M18">
         <v>4</v>
       </c>
-      <c r="M18">
-        <v>6</v>
-      </c>
       <c r="N18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -2036,10 +2220,10 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2051,13 +2235,13 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>6</v>
@@ -2065,10 +2249,22 @@
       <c r="AC18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:29">
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>6</v>
+      </c>
+      <c r="AF18">
+        <v>6</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2092,46 +2288,46 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2140,24 +2336,36 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>7</v>
+      </c>
+      <c r="AF19">
+        <v>5</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2181,22 +2389,22 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -2205,17 +2413,17 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
         <v>4</v>
       </c>
-      <c r="S20">
-        <v>5</v>
-      </c>
-      <c r="T20">
-        <v>5</v>
-      </c>
       <c r="U20">
         <v>5</v>
       </c>
@@ -2229,7 +2437,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2243,10 +2451,22 @@
       <c r="AC20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>5</v>
+      </c>
+      <c r="AF20">
+        <v>5</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -2270,43 +2490,43 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2315,27 +2535,39 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>6</v>
+      </c>
+      <c r="AE21">
+        <v>7</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -2359,13 +2591,13 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2380,13 +2612,13 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2407,7 +2639,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2420,14 +2652,26 @@
       </c>
       <c r="AC22">
         <v>5</v>
+      </c>
+      <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
+        <v>5</v>
+      </c>
+      <c r="AF22">
+        <v>5</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2435,16 +2679,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2452,26 +2696,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2497,56 +2744,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>90</v>
@@ -2570,17 +2826,17 @@
         <v>90</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>95</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>95.5</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
       <c r="M4">
         <v>100</v>
       </c>
@@ -2588,33 +2844,42 @@
         <v>100</v>
       </c>
       <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
         <v>95</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>96.8</v>
       </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>96.90000000000001</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>80</v>
@@ -2638,51 +2903,60 @@
         <v>75</v>
       </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>85</v>
       </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>88.59999999999999</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>96.90000000000001</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>95</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>82.5</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>87.5</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>97.90000000000001</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>95</v>
       </c>
-      <c r="U5">
-        <v>100</v>
-      </c>
-      <c r="V5">
+      <c r="W5">
+        <v>100</v>
+      </c>
+      <c r="X5">
         <v>84.09999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -2706,11 +2980,11 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>95</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
         <v>100</v>
       </c>
@@ -2727,14 +3001,14 @@
         <v>100</v>
       </c>
       <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>96.8</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
-        <v>100</v>
-      </c>
       <c r="S6">
         <v>100</v>
       </c>
@@ -2745,12 +3019,21 @@
         <v>100</v>
       </c>
       <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="X6">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -2813,12 +3096,21 @@
         <v>100</v>
       </c>
       <c r="V7">
+        <v>100</v>
+      </c>
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>90</v>
@@ -2842,17 +3134,17 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>95.5</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
@@ -2863,30 +3155,39 @@
         <v>100</v>
       </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>93.5</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>95.3</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>96.7</v>
       </c>
-      <c r="U8">
-        <v>100</v>
-      </c>
-      <c r="V8">
+      <c r="W8">
+        <v>100</v>
+      </c>
+      <c r="X8">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>90</v>
@@ -2910,11 +3211,11 @@
         <v>100</v>
       </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>90</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
       <c r="K9">
         <v>100</v>
       </c>
@@ -2931,30 +3232,39 @@
         <v>100</v>
       </c>
       <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>93.5</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
-        <v>100</v>
-      </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>98.3</v>
       </c>
-      <c r="U9">
-        <v>100</v>
-      </c>
-      <c r="V9">
+      <c r="W9">
+        <v>100</v>
+      </c>
+      <c r="X9">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -3017,12 +3327,21 @@
         <v>100</v>
       </c>
       <c r="V10">
+        <v>100</v>
+      </c>
+      <c r="W10">
+        <v>100</v>
+      </c>
+      <c r="X10">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>90</v>
@@ -3046,51 +3365,60 @@
         <v>75</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>90</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>83.3</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>72.7</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>50</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>85</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>37.5</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>93.5</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>88.90000000000001</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>50</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>33.3</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>56.7</v>
       </c>
-      <c r="U11">
-        <v>100</v>
-      </c>
-      <c r="V11">
+      <c r="W11">
+        <v>100</v>
+      </c>
+      <c r="X11">
         <v>23.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>70</v>
@@ -3114,51 +3442,60 @@
         <v>80</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>70</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>90.90000000000001</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>93.8</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>92.5</v>
       </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
       <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
         <v>80</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>80.59999999999999</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>89.09999999999999</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>95.8</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>93.3</v>
       </c>
-      <c r="U12">
-        <v>100</v>
-      </c>
-      <c r="V12">
+      <c r="W12">
+        <v>100</v>
+      </c>
+      <c r="X12">
         <v>82.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -3182,51 +3519,60 @@
         <v>80</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>95</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
         <v>90.59999999999999</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>97.5</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
       <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>85</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>96.8</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
       <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
         <v>93.8</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>96.7</v>
       </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
-      <c r="V13">
+      <c r="W13">
+        <v>100</v>
+      </c>
+      <c r="X13">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>90</v>
@@ -3250,17 +3596,17 @@
         <v>95</v>
       </c>
       <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
         <v>90</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>95.5</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
@@ -3268,33 +3614,42 @@
         <v>100</v>
       </c>
       <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
         <v>92.5</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>93.5</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>95.3</v>
       </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-      <c r="T14">
-        <v>100</v>
-      </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
+        <v>100</v>
+      </c>
+      <c r="X14">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>70</v>
@@ -3318,17 +3673,17 @@
         <v>75</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>70</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>95.5</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
       <c r="M15">
         <v>100</v>
       </c>
@@ -3336,33 +3691,42 @@
         <v>100</v>
       </c>
       <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
         <v>82.5</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>80.59999999999999</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>95.3</v>
       </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-      <c r="T15">
-        <v>100</v>
-      </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
+        <v>100</v>
+      </c>
+      <c r="W15">
+        <v>100</v>
+      </c>
+      <c r="X15">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>90</v>
@@ -3386,17 +3750,17 @@
         <v>90</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>90</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>95.5</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
         <v>100</v>
       </c>
@@ -3404,33 +3768,42 @@
         <v>100</v>
       </c>
       <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
         <v>95</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>93.5</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>95.3</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
+        <v>100</v>
+      </c>
+      <c r="W16">
+        <v>100</v>
+      </c>
+      <c r="X16">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -3454,51 +3827,60 @@
         <v>100</v>
       </c>
       <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
         <v>90</v>
       </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>97.7</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>96.90000000000001</v>
       </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>95</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>93.5</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>98.40000000000001</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>97.90000000000001</v>
       </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
-      <c r="U17">
-        <v>100</v>
-      </c>
       <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
+        <v>100</v>
+      </c>
+      <c r="X17">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -3522,11 +3904,11 @@
         <v>90</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>90</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
         <v>100</v>
       </c>
@@ -3540,33 +3922,42 @@
         <v>100</v>
       </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>95</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>93.5</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>98.3</v>
       </c>
-      <c r="U18">
-        <v>100</v>
-      </c>
-      <c r="V18">
+      <c r="W18">
+        <v>100</v>
+      </c>
+      <c r="X18">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -3590,17 +3981,17 @@
         <v>85</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>85</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>93.2</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
         <v>100</v>
       </c>
@@ -3608,33 +3999,42 @@
         <v>100</v>
       </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>85</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>87.09999999999999</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>92.2</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
-        <v>100</v>
-      </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
+        <v>100</v>
+      </c>
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>70</v>
@@ -3658,17 +4058,17 @@
         <v>75</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>70</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>88.59999999999999</v>
       </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
         <v>100</v>
       </c>
@@ -3676,33 +4076,42 @@
         <v>100</v>
       </c>
       <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
         <v>80</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>77.40000000000001</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>78.09999999999999</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>70.8</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>95</v>
       </c>
-      <c r="U20">
-        <v>100</v>
-      </c>
-      <c r="V20">
+      <c r="W20">
+        <v>100</v>
+      </c>
+      <c r="X20">
         <v>50.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -3726,51 +4135,60 @@
         <v>100</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>90</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>97.7</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>96.90000000000001</v>
       </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
         <v>97.5</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>93.5</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>96.90000000000001</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>97.90000000000001</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>96.7</v>
       </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
-      <c r="V21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="X21">
+        <v>100</v>
+      </c>
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -3794,53 +4212,62 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>85</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>93.2</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>90.59999999999999</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>95</v>
       </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
       <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
         <v>92.5</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>90.3</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>95.3</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>93.8</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>91.7</v>
       </c>
-      <c r="U22">
-        <v>100</v>
-      </c>
-      <c r="V22">
+      <c r="W22">
+        <v>100</v>
+      </c>
+      <c r="X22">
         <v>90.5</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3861,31 +4288,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4114,21 +4541,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4163,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4197,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -824,22 +824,22 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -925,22 +925,22 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF5">
         <v>5</v>
@@ -1026,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1127,16 +1127,16 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD7">
         <v>10</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1231,19 +1231,19 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1329,25 +1329,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA9">
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1430,25 +1430,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>10</v>
       </c>
       <c r="AE10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1632,22 +1632,22 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <v>5</v>
@@ -1733,25 +1733,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1834,25 +1834,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1935,25 +1935,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2036,22 +2036,22 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF16">
         <v>5</v>
@@ -2137,25 +2137,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2241,22 +2241,22 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2345,16 +2345,16 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -2541,25 +2541,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -4338,7 +4338,7 @@
         <v>47.4</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>31.6</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>26.3</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>21.1</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         <v>21.1</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         <v>15.8</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>15.8</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1EV - Estadisticos 20231.xlsx
+++ b/grupos/1EV - Estadisticos 20231.xlsx
@@ -824,22 +824,22 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -925,22 +925,22 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF5">
         <v>5</v>
@@ -1026,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1127,16 +1127,16 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>10</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1231,19 +1231,19 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1329,25 +1329,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1430,25 +1430,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>10</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1632,22 +1632,22 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF12">
         <v>5</v>
@@ -1733,25 +1733,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1834,25 +1834,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1935,25 +1935,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2036,22 +2036,22 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <v>5</v>
@@ -2137,25 +2137,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2241,22 +2241,22 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2345,16 +2345,16 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -2541,25 +2541,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -4338,7 +4338,7 @@
         <v>47.4</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>31.6</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>26.3</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>21.1</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         <v>21.1</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         <v>15.8</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>15.8</v>
       </c>
       <c r="H8">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
